--- a/public/informes-templates/INFORME DE DIAGNOSTICO SERVOMOTOR.xlsx
+++ b/public/informes-templates/INFORME DE DIAGNOSTICO SERVOMOTOR.xlsx
@@ -1,53 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SIP-APP\SIPAPP-HUAQUIAN\Frontend\public\informes-templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B1677B-6417-4914-8082-E108CA5A2BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E8DB7E-4581-47F5-B686-B62B84DCB7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="YKtGdDFrA4F8jWsusKreyu2IQn0Y6uPLGSxctRv6/Zs="/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>INFORME DE SERVICIO</t>
   </si>
@@ -107,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">OBSERVACION </t>
-  </si>
-  <si>
-    <t>El equipo ingreso contaminado.</t>
   </si>
   <si>
     <t>FOTOS DEL EQUIPO</t>
@@ -226,9 +191,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -478,10 +444,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+  <cellXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -503,62 +467,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -569,14 +485,89 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,68 +586,53 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -861,22 +837,22 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z224"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="18.5" customWidth="1"/>
+    <col min="1" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="11"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -896,15 +872,15 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29"/>
+    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="13"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -924,19 +900,17 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="31" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B3" s="11"/>
+    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="11"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -956,17 +930,17 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
       <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="11"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -986,17 +960,17 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="11"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -1016,17 +990,17 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
+    <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
       <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="11"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1046,17 +1020,17 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
+    <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="11"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1076,17 +1050,17 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
+    <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="11"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1106,17 +1080,17 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
+    <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="11"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1136,17 +1110,17 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
+    <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="11"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1166,17 +1140,17 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
+    <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="18"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="9"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1196,15 +1170,15 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
+    <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1224,19 +1198,19 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="32" t="s">
+    <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="17" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="9"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1256,9 +1230,9 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
+    <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1296,9 +1270,9 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
+    <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1324,21 +1298,19 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="29"/>
+    <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="9"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1358,17 +1330,17 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15" t="s">
-        <v>21</v>
+    <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>20</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="9"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1388,15 +1360,15 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="11"/>
+    <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1416,15 +1388,15 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
+    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="34"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1444,15 +1416,15 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
+    <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="34"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1472,15 +1444,15 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13"/>
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="34"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1500,15 +1472,15 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
+    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="39"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1528,15 +1500,15 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
+    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="39"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1556,15 +1528,15 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
+    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="34"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="39"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1584,15 +1556,15 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
+    <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="39"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1612,15 +1584,15 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
+    <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="34"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1640,15 +1612,15 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
+    <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="34"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1668,15 +1640,15 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="13"/>
+    <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="34"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="39"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1696,15 +1668,15 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
+    <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="34"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1724,23 +1696,23 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="20"/>
+      <c r="E30" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="20"/>
+      <c r="G30" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="9"/>
+      <c r="H30" s="20"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1760,15 +1732,15 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="11"/>
+    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="32"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="33"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1788,15 +1760,15 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="13"/>
+    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1816,15 +1788,15 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
+    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="34"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="35"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1844,15 +1816,15 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="13"/>
+    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="34"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1872,15 +1844,15 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="13"/>
+    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="34"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1900,15 +1872,15 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="13"/>
+    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="34"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="35"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -1928,15 +1900,15 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="13"/>
+    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="34"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="35"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -1956,15 +1928,15 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13"/>
+    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="34"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="35"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -1984,15 +1956,15 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13"/>
+    <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="34"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="35"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2012,15 +1984,15 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13"/>
+    <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="34"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="35"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2040,15 +2012,15 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="13"/>
+    <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="34"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="35"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2068,15 +2040,15 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="13"/>
+    <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="34"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="35"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2096,23 +2068,23 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A43" s="8" t="s">
+    <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="8" t="s">
+      <c r="D43" s="20"/>
+      <c r="E43" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="14" t="s">
+      <c r="F43" s="10"/>
+      <c r="G43" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="H43" s="11"/>
+      <c r="H43" s="10"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2132,17 +2104,17 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>30</v>
+    <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>29</v>
       </c>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="9"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="20"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2162,19 +2134,19 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="17" t="s">
-        <v>31</v>
+      <c r="B45" s="23" t="s">
+        <v>30</v>
       </c>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="9"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="20"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2194,15 +2166,15 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
       <c r="B46" s="18"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="9"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="20"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -2222,15 +2194,15 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="18"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="9"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="20"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2250,15 +2222,15 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="18"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="9"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="20"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2278,15 +2250,15 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="18"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="9"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="20"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2306,17 +2278,17 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
-        <v>32</v>
+    <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>31</v>
       </c>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="9"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="20"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2336,20 +2308,20 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -2370,18 +2342,18 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>1</v>
       </c>
-      <c r="B52" s="19" t="s">
-        <v>36</v>
+      <c r="B52" s="25" t="s">
+        <v>35</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="9"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="20"/>
       <c r="H52" s="7"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -2402,18 +2374,18 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>2</v>
       </c>
-      <c r="B53" s="19" t="s">
-        <v>37</v>
+      <c r="B53" s="25" t="s">
+        <v>36</v>
       </c>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="9"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="20"/>
       <c r="H53" s="7"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -2434,18 +2406,18 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>3</v>
       </c>
-      <c r="B54" s="19" t="s">
-        <v>38</v>
+      <c r="B54" s="25" t="s">
+        <v>37</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="9"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
       <c r="H54" s="7"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -2466,18 +2438,18 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>4</v>
       </c>
-      <c r="B55" s="19" t="s">
-        <v>39</v>
+      <c r="B55" s="25" t="s">
+        <v>38</v>
       </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="9"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="20"/>
       <c r="H55" s="7"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -2498,18 +2470,18 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>5</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>40</v>
+      <c r="B56" s="25" t="s">
+        <v>39</v>
       </c>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="9"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="20"/>
       <c r="H56" s="7"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -2530,18 +2502,18 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>6</v>
       </c>
-      <c r="B57" s="19" t="s">
-        <v>41</v>
+      <c r="B57" s="25" t="s">
+        <v>40</v>
       </c>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="9"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="20"/>
       <c r="H57" s="7"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -2562,18 +2534,18 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>7</v>
       </c>
-      <c r="B58" s="19" t="s">
-        <v>42</v>
+      <c r="B58" s="25" t="s">
+        <v>41</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="9"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="20"/>
       <c r="H58" s="7"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -2594,18 +2566,18 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>8</v>
       </c>
-      <c r="B59" s="19" t="s">
-        <v>43</v>
+      <c r="B59" s="25" t="s">
+        <v>42</v>
       </c>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="9"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="20"/>
       <c r="H59" s="7"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -2626,18 +2598,18 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>9</v>
       </c>
-      <c r="B60" s="19" t="s">
-        <v>44</v>
+      <c r="B60" s="25" t="s">
+        <v>43</v>
       </c>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="9"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="20"/>
       <c r="H60" s="7"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -2658,18 +2630,18 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>10</v>
       </c>
-      <c r="B61" s="19" t="s">
-        <v>45</v>
+      <c r="B61" s="25" t="s">
+        <v>44</v>
       </c>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="9"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="20"/>
       <c r="H61" s="7"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -2690,18 +2662,18 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>11</v>
       </c>
-      <c r="B62" s="19" t="s">
-        <v>46</v>
+      <c r="B62" s="25" t="s">
+        <v>45</v>
       </c>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="9"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="20"/>
       <c r="H62" s="7"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -2722,18 +2694,18 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>12</v>
       </c>
-      <c r="B63" s="19" t="s">
-        <v>47</v>
+      <c r="B63" s="25" t="s">
+        <v>46</v>
       </c>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="9"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
+      <c r="G63" s="20"/>
       <c r="H63" s="7"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -2754,18 +2726,18 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>13</v>
       </c>
-      <c r="B64" s="19" t="s">
-        <v>48</v>
+      <c r="B64" s="25" t="s">
+        <v>47</v>
       </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="9"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="20"/>
       <c r="H64" s="7"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -2786,17 +2758,17 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A65" s="22" t="s">
-        <v>49</v>
+    <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="29" t="s">
+        <v>48</v>
       </c>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="9"/>
+      <c r="B65" s="19"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
+      <c r="G65" s="19"/>
+      <c r="H65" s="20"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2816,17 +2788,17 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A66" s="20" t="s">
-        <v>50</v>
+    <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="30" t="s">
+        <v>49</v>
       </c>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-      <c r="H66" s="9"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="20"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2846,17 +2818,17 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A67" s="20" t="s">
-        <v>51</v>
+    <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="30" t="s">
+        <v>50</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="9"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="20"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -2876,17 +2848,17 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A68" s="20" t="s">
-        <v>52</v>
+    <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="30" t="s">
+        <v>51</v>
       </c>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="9"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="20"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -2906,17 +2878,17 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A69" s="22" t="s">
-        <v>53</v>
+    <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
+        <v>52</v>
       </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="9"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="20"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -2936,17 +2908,17 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A70" s="20" t="s">
-        <v>54</v>
+    <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="30" t="s">
+        <v>53</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="9"/>
+      <c r="B70" s="19"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19"/>
+      <c r="E70" s="19"/>
+      <c r="F70" s="19"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="20"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -2966,17 +2938,17 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
-        <v>51</v>
+    <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="30" t="s">
+        <v>50</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="9"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="19"/>
+      <c r="F71" s="19"/>
+      <c r="G71" s="19"/>
+      <c r="H71" s="20"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -2996,17 +2968,17 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
-        <v>55</v>
+    <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="30" t="s">
+        <v>54</v>
       </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="9"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="19"/>
+      <c r="F72" s="19"/>
+      <c r="G72" s="19"/>
+      <c r="H72" s="20"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -3026,17 +2998,17 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A73" s="21" t="s">
-        <v>56</v>
+    <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="31" t="s">
+        <v>55</v>
       </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="9"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="20"/>
       <c r="I73" s="6"/>
       <c r="J73" s="6"/>
       <c r="K73" s="6"/>
@@ -3056,7 +3028,7 @@
       <c r="Y73" s="6"/>
       <c r="Z73" s="6"/>
     </row>
-    <row r="74" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3084,7 +3056,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3112,7 +3084,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3140,7 +3112,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3168,7 +3140,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3196,7 +3168,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3224,7 +3196,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3252,7 +3224,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3280,7 +3252,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3308,7 +3280,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3336,7 +3308,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3364,7 +3336,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3392,7 +3364,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3420,7 +3392,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3448,7 +3420,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3476,7 +3448,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3504,7 +3476,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3532,7 +3504,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3560,7 +3532,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3588,7 +3560,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3616,7 +3588,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3644,7 +3616,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3672,7 +3644,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3700,7 +3672,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3728,7 +3700,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3756,7 +3728,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3784,7 +3756,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3812,7 +3784,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3840,7 +3812,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3868,7 +3840,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3896,7 +3868,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3924,7 +3896,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3952,7 +3924,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3980,7 +3952,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -4008,7 +3980,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -4036,7 +4008,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -4064,7 +4036,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -4092,7 +4064,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -4120,7 +4092,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -4148,7 +4120,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -4176,7 +4148,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -4204,7 +4176,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -4232,7 +4204,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -4260,7 +4232,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -4288,7 +4260,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -4316,7 +4288,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -4344,7 +4316,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -4372,7 +4344,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -4400,7 +4372,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -4428,7 +4400,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -4456,7 +4428,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -4484,7 +4456,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -4512,7 +4484,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -4540,7 +4512,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -4568,7 +4540,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -4596,7 +4568,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -4624,7 +4596,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -4652,7 +4624,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -4680,7 +4652,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -4708,7 +4680,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -4736,7 +4708,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -4764,7 +4736,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -4792,7 +4764,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4820,7 +4792,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4848,7 +4820,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4876,7 +4848,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4904,7 +4876,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4932,7 +4904,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4960,7 +4932,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4988,7 +4960,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -5016,7 +4988,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -5044,7 +5016,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -5072,7 +5044,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -5100,7 +5072,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -5128,7 +5100,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -5156,7 +5128,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -5184,7 +5156,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -5212,7 +5184,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -5240,7 +5212,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -5268,7 +5240,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -5296,7 +5268,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -5324,7 +5296,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -5352,7 +5324,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -5380,7 +5352,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -5408,7 +5380,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -5436,7 +5408,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -5464,7 +5436,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -5492,7 +5464,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -5520,7 +5492,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -5548,7 +5520,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -5576,7 +5548,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -5604,7 +5576,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -5632,7 +5604,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -5660,7 +5632,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -5688,7 +5660,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -5716,7 +5688,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -5744,7 +5716,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -5772,7 +5744,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -5800,7 +5772,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -5828,7 +5800,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -5856,7 +5828,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -5884,7 +5856,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -5912,7 +5884,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -5940,7 +5912,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -5968,7 +5940,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -5996,7 +5968,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -6024,7 +5996,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -6052,7 +6024,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -6080,7 +6052,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -6108,7 +6080,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -6136,7 +6108,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -6164,7 +6136,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -6192,7 +6164,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -6220,7 +6192,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -6248,7 +6220,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -6276,7 +6248,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -6304,7 +6276,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -6332,7 +6304,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -6360,7 +6332,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -6388,7 +6360,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -6416,7 +6388,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -6444,7 +6416,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -6472,7 +6444,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -6500,7 +6472,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -6528,7 +6500,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -6556,7 +6528,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -6584,7 +6556,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -6612,7 +6584,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -6640,7 +6612,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -6668,7 +6640,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -6696,7 +6668,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -6724,7 +6696,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -6752,7 +6724,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -6780,7 +6752,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -6808,7 +6780,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -6836,7 +6808,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -6864,7 +6836,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -6892,7 +6864,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -6920,7 +6892,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -6948,7 +6920,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -6976,7 +6948,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -7004,7 +6976,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -7032,7 +7004,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -7060,7 +7032,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -7088,7 +7060,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -7116,7 +7088,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -7144,7 +7116,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -7172,7 +7144,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -7200,7 +7172,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -7228,7 +7200,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -7256,7 +7228,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -7285,73 +7257,66 @@
       <c r="Z224" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="A18:B29"/>
-    <mergeCell ref="C18:D29"/>
-    <mergeCell ref="E18:F29"/>
-    <mergeCell ref="G18:H29"/>
+  <mergeCells count="55">
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:G64"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A13:B16"/>
+    <mergeCell ref="C13:H13"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:B11"/>
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="A13:B16"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="G31:H42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B42"/>
-    <mergeCell ref="C31:D42"/>
-    <mergeCell ref="E31:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/informes-templates/INFORME DE DIAGNOSTICO SERVOMOTOR.xlsx
+++ b/public/informes-templates/INFORME DE DIAGNOSTICO SERVOMOTOR.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E8DB7E-4581-47F5-B686-B62B84DCB7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14ADDE1D-1D1E-4576-90C1-B45FC5B596E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,39 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -164,32 +137,14 @@
     <t>OBSEVACIONES DEL EQUIPO  O CAUSAS DE POSIBLES FALLAS</t>
   </si>
   <si>
-    <t>1)</t>
-  </si>
-  <si>
-    <t>2)</t>
-  </si>
-  <si>
-    <t>3)</t>
-  </si>
-  <si>
     <t>ACTIVIDADES A REALIZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3) </t>
-  </si>
-  <si>
-    <t>4)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,22 +172,8 @@
     <font>
       <b/>
       <i/>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -262,8 +203,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,8 +235,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -431,20 +384,37 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -452,50 +422,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -506,67 +440,148 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -584,55 +599,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -836,23 +802,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z224"/>
+  <dimension ref="A1:Z220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="20"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -873,14 +839,14 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="13"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="25"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -901,16 +867,14 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="10"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -931,16 +895,14 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -961,16 +923,16 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="44" t="s">
+        <v>2</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="10"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -991,16 +953,26 @@
       <c r="Z5" s="1"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1021,16 +993,14 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="10"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1051,16 +1021,18 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="37" t="s">
+        <v>9</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1081,16 +1053,16 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
+      <c r="A9" s="35" t="s">
+        <v>11</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="10"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1111,16 +1083,14 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="50"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1141,16 +1111,14 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1171,14 +1139,14 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1199,18 +1167,14 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1231,26 +1195,14 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1271,14 +1223,14 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1299,18 +1251,14 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="16"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="20"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="54"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1331,16 +1279,14 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
+      <c r="A17" s="51"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="54"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1361,14 +1307,14 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="A18" s="51"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
+      <c r="H18" s="54"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1389,14 +1335,14 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="39"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="54"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1417,14 +1363,14 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1445,14 +1391,14 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="39"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="56"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1473,14 +1419,22 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
+      <c r="A22" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="11"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1501,14 +1455,14 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="34"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="39"/>
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1529,14 +1483,14 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="34"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="52"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1557,14 +1511,14 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="39"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="52"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1585,14 +1539,14 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="39"/>
+      <c r="A26" s="51"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="52"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -1613,14 +1567,14 @@
       <c r="Z26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="52"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -1641,14 +1595,14 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="52"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1669,14 +1623,14 @@
       <c r="Z28" s="1"/>
     </row>
     <row r="29" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="34"/>
-      <c r="B29" s="35"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="52"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1697,22 +1651,14 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="20"/>
-      <c r="G30" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="20"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="52"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1732,15 +1678,15 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="32"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="33"/>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="52"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1760,15 +1706,15 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="51"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="52"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1788,15 +1734,15 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="34"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="35"/>
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="52"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1816,15 +1762,15 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="34"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35"/>
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="51"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="52"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1844,15 +1790,23 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35"/>
+    <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="20"/>
+      <c r="G35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="20"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -1872,15 +1826,17 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
+    <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -1900,15 +1856,19 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="34"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35"/>
+    <row r="37" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -1928,15 +1888,15 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="34"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
+    <row r="38" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="11"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -1957,14 +1917,14 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="34"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="35"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="11"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -1985,14 +1945,14 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="34"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="35"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="8"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2013,14 +1973,14 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="34"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="35"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="11"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2041,14 +2001,14 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="34"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="35"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="11"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2069,22 +2029,16 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="27" t="s">
-        <v>25</v>
+      <c r="A43" s="15" t="s">
+        <v>22</v>
       </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="28" t="s">
-        <v>27</v>
-      </c>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
       <c r="F43" s="10"/>
-      <c r="G43" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="11"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2105,16 +2059,20 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
-        <v>29</v>
+      <c r="A44" s="2" t="s">
+        <v>23</v>
       </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="20"/>
+      <c r="B44" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2135,18 +2093,18 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>8</v>
+      <c r="A45" s="5">
+        <v>1</v>
       </c>
-      <c r="B45" s="23" t="s">
-        <v>30</v>
+      <c r="B45" s="14" t="s">
+        <v>26</v>
       </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="20"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="5"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2167,14 +2125,18 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="20"/>
+      <c r="A46" s="5">
+        <v>2</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="5"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -2195,14 +2157,18 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="20"/>
+      <c r="A47" s="5">
+        <v>3</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="5"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2223,14 +2189,18 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="20"/>
+      <c r="A48" s="5">
+        <v>4</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="5"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2251,14 +2221,18 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="20"/>
+      <c r="A49" s="5">
+        <v>5</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="5"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2279,16 +2253,18 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
+      <c r="A50" s="5">
+        <v>6</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="20"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="5"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2309,20 +2285,18 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="5">
+        <v>7</v>
+      </c>
+      <c r="B51" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B51" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="5"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2343,18 +2317,18 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>1</v>
+      <c r="A52" s="5">
+        <v>8</v>
       </c>
-      <c r="B52" s="25" t="s">
-        <v>35</v>
+      <c r="B52" s="14" t="s">
+        <v>33</v>
       </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="7"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="5"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2375,18 +2349,18 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
-        <v>2</v>
+      <c r="A53" s="5">
+        <v>9</v>
       </c>
-      <c r="B53" s="25" t="s">
-        <v>36</v>
+      <c r="B53" s="14" t="s">
+        <v>34</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="7"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="5"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2407,18 +2381,18 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
-        <v>3</v>
+      <c r="A54" s="5">
+        <v>10</v>
       </c>
-      <c r="B54" s="25" t="s">
-        <v>37</v>
+      <c r="B54" s="14" t="s">
+        <v>35</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="7"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="5"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2439,18 +2413,18 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
-        <v>4</v>
+      <c r="A55" s="5">
+        <v>11</v>
       </c>
-      <c r="B55" s="25" t="s">
-        <v>38</v>
+      <c r="B55" s="14" t="s">
+        <v>36</v>
       </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="7"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="5"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2471,18 +2445,18 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
-        <v>5</v>
+      <c r="A56" s="5">
+        <v>12</v>
       </c>
-      <c r="B56" s="25" t="s">
-        <v>39</v>
+      <c r="B56" s="14" t="s">
+        <v>37</v>
       </c>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="7"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="5"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -2503,18 +2477,18 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
-        <v>6</v>
+      <c r="A57" s="5">
+        <v>13</v>
       </c>
-      <c r="B57" s="25" t="s">
-        <v>40</v>
+      <c r="B57" s="14" t="s">
+        <v>38</v>
       </c>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="7"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="11"/>
+      <c r="H57" s="5"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
@@ -2535,18 +2509,16 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>7</v>
+      <c r="A58" s="13" t="s">
+        <v>39</v>
       </c>
-      <c r="B58" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="7"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2567,18 +2539,14 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
-        <v>8</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="7"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="11"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2599,18 +2567,14 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
-        <v>9</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="7"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="11"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2631,18 +2595,14 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
-        <v>10</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="7"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="11"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2663,18 +2623,14 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>11</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="7"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="11"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2695,18 +2651,14 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
-        <v>12</v>
-      </c>
-      <c r="B63" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="7"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="11"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2727,18 +2679,16 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
-        <v>13</v>
+      <c r="A64" s="13" t="s">
+        <v>40</v>
       </c>
-      <c r="B64" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="7"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="11"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2759,16 +2709,14 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="20"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="11"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2789,16 +2737,14 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="20"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="11"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2819,16 +2765,14 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="20"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="11"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -2849,16 +2793,14 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="20"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="10"/>
+      <c r="H68" s="11"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -2879,46 +2821,42 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
-      <c r="W69" s="1"/>
-      <c r="X69" s="1"/>
-      <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
     </row>
     <row r="70" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="20"/>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -2939,16 +2877,14 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="20"/>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -2969,16 +2905,14 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="20"/>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
@@ -2999,34 +2933,32 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="6"/>
-      <c r="S73" s="6"/>
-      <c r="T73" s="6"/>
-      <c r="U73" s="6"/>
-      <c r="V73" s="6"/>
-      <c r="W73" s="6"/>
-      <c r="X73" s="6"/>
-      <c r="Y73" s="6"/>
-      <c r="Z73" s="6"/>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
+      <c r="O73" s="1"/>
+      <c r="P73" s="1"/>
+      <c r="Q73" s="1"/>
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
@@ -7144,179 +7076,63 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="1"/>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
-      <c r="F221" s="1"/>
-      <c r="G221" s="1"/>
-      <c r="H221" s="1"/>
-      <c r="I221" s="1"/>
-      <c r="J221" s="1"/>
-      <c r="K221" s="1"/>
-      <c r="L221" s="1"/>
-      <c r="M221" s="1"/>
-      <c r="N221" s="1"/>
-      <c r="O221" s="1"/>
-      <c r="P221" s="1"/>
-      <c r="Q221" s="1"/>
-      <c r="R221" s="1"/>
-      <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
-      <c r="U221" s="1"/>
-      <c r="V221" s="1"/>
-      <c r="W221" s="1"/>
-      <c r="X221" s="1"/>
-      <c r="Y221" s="1"/>
-      <c r="Z221" s="1"/>
-    </row>
-    <row r="222" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="1"/>
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
-      <c r="E222" s="1"/>
-      <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
-      <c r="H222" s="1"/>
-      <c r="I222" s="1"/>
-      <c r="J222" s="1"/>
-      <c r="K222" s="1"/>
-      <c r="L222" s="1"/>
-      <c r="M222" s="1"/>
-      <c r="N222" s="1"/>
-      <c r="O222" s="1"/>
-      <c r="P222" s="1"/>
-      <c r="Q222" s="1"/>
-      <c r="R222" s="1"/>
-      <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
-      <c r="U222" s="1"/>
-      <c r="V222" s="1"/>
-      <c r="W222" s="1"/>
-      <c r="X222" s="1"/>
-      <c r="Y222" s="1"/>
-      <c r="Z222" s="1"/>
-    </row>
-    <row r="223" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="1"/>
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
-      <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1"/>
-      <c r="J223" s="1"/>
-      <c r="K223" s="1"/>
-      <c r="L223" s="1"/>
-      <c r="M223" s="1"/>
-      <c r="N223" s="1"/>
-      <c r="O223" s="1"/>
-      <c r="P223" s="1"/>
-      <c r="Q223" s="1"/>
-      <c r="R223" s="1"/>
-      <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
-      <c r="U223" s="1"/>
-      <c r="V223" s="1"/>
-      <c r="W223" s="1"/>
-      <c r="X223" s="1"/>
-      <c r="Y223" s="1"/>
-      <c r="Z223" s="1"/>
-    </row>
-    <row r="224" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="1"/>
-      <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
-      <c r="E224" s="1"/>
-      <c r="F224" s="1"/>
-      <c r="G224" s="1"/>
-      <c r="H224" s="1"/>
-      <c r="I224" s="1"/>
-      <c r="J224" s="1"/>
-      <c r="K224" s="1"/>
-      <c r="L224" s="1"/>
-      <c r="M224" s="1"/>
-      <c r="N224" s="1"/>
-      <c r="O224" s="1"/>
-      <c r="P224" s="1"/>
-      <c r="Q224" s="1"/>
-      <c r="R224" s="1"/>
-      <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
-      <c r="U224" s="1"/>
-      <c r="V224" s="1"/>
-      <c r="W224" s="1"/>
-      <c r="X224" s="1"/>
-      <c r="Y224" s="1"/>
-      <c r="Z224" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:G64"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="A50:H50"/>
+  <mergeCells count="52">
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
     <mergeCell ref="B51:G51"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="B53:G53"/>
     <mergeCell ref="B54:G54"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:B16"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A67:H67"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>